--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -2,87 +2,91 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5aff7921ae384045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rde8dcda7138b4940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Rd095384548d944d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R5465a01fbbbe4161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Ra64ce926e2fd42cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R742742c1e8494778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R7b331280ec2c419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R0ac102763f024129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R046db721908b435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R20d37df8e36642c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R3062d2db795c46ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R6f18bee4c6ea4b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Rf80a9cfc65864523"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R659c424eba2d48d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="Rbc536bce6e274dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R5b4576067caf494e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R1b60a9341d7d450c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="Ra84c098767c549ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R590e680eb5e74170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="R4c68f8f7d53e4d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R47cdec2c3af84c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="Ra9f58a50ed9744e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R9bc80e63821e4199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0045" sheetId="24" r:id="R5fbcf13658df4f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0046" sheetId="25" r:id="Rce74efe197194f2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0047" sheetId="26" r:id="R5ac7c623c834444b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0048" sheetId="27" r:id="R8c779ff316b04e3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0049" sheetId="28" r:id="R26a0c370ce884580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0050" sheetId="29" r:id="Rbacde1c9e8d44966"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0051" sheetId="30" r:id="R3d1cea75d08047bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0052" sheetId="31" r:id="R1c8fc70d3118439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0053" sheetId="32" r:id="Rab5fdd6eecaa45a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0054" sheetId="33" r:id="R150efa0ba0fe43ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0055" sheetId="34" r:id="R7e0b003b70934d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0056" sheetId="35" r:id="Rf476d1cf9cb74f04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0057" sheetId="36" r:id="R238abeefe196463e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0058" sheetId="37" r:id="Rd88c6f0784e3415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0059" sheetId="38" r:id="R724971c24683482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0060" sheetId="39" r:id="Rcdf13d1e61ef45f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0061" sheetId="40" r:id="Ra376d5e732ee4e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0062" sheetId="41" r:id="R028f88f5bfd64806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0063" sheetId="42" r:id="R6727125b82434172"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0064" sheetId="43" r:id="Rc8bd8d719c704d43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0065" sheetId="44" r:id="R87c899f8668e4e92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0066" sheetId="45" r:id="R151cae7ca26c46ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0067" sheetId="46" r:id="Rdd13264d73c74109"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0068" sheetId="47" r:id="Rfb2d5334e5024e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0069" sheetId="48" r:id="Rfa01fe7ee4ca4fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0070" sheetId="49" r:id="Rbdb6c4180bd9418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0071" sheetId="50" r:id="Ra638b72e9b9a4c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0072" sheetId="51" r:id="Re8c6c506e30b48fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0073" sheetId="52" r:id="Ra35a490a3e3f4766"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0074" sheetId="53" r:id="Rf2c7af50d6434ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0075" sheetId="54" r:id="R8f6bffd8c6a446fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0076" sheetId="55" r:id="Rc003ecb8f4d648fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0077" sheetId="56" r:id="R505e51a394224a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0078" sheetId="57" r:id="Ra070d571c62942eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0079" sheetId="58" r:id="R990cc1c289b54f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0080" sheetId="59" r:id="Ra03c51dafd8a4539"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0081" sheetId="60" r:id="R229c0f391f584c41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0082" sheetId="61" r:id="R6b59e15f0cc44f7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0083" sheetId="62" r:id="Ra5c8f255c518417c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0084" sheetId="63" r:id="R8c30b794ec854e51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0085" sheetId="64" r:id="Rf90cdbff488a46a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Directory" sheetId="65" r:id="R13a458082b524c47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0086" sheetId="66" r:id="R7e0e2f52d8634619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0087" sheetId="67" r:id="Ra91a20d64fcd4804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0088" sheetId="68" r:id="Rccb8b9e1ca684eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0089" sheetId="69" r:id="R1996a9c7ac2645eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0090" sheetId="70" r:id="R1a7cf5eb25d54901"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0091" sheetId="71" r:id="R86c20343f7b94df8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0092" sheetId="72" r:id="R9ee24471270b460a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0093" sheetId="73" r:id="R09bd756a234642fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0094" sheetId="74" r:id="R22c72c274e6547e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0095" sheetId="75" r:id="Rc19e60dbc0a34392"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0096" sheetId="76" r:id="R91eaffe6c5354538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0097" sheetId="77" r:id="Rb3e8bc72b1ab42af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0098" sheetId="78" r:id="R7fbb4fead79043dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0099" sheetId="79" r:id="R1f06322629004056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0100" sheetId="80" r:id="R803b34e8bca14e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0101" sheetId="81" r:id="R831be6d4d54b433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R92aa8d4ae6e24fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R9c8ed503c7c442bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Ra6e97c587a784c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Re730e49131494efb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rb740bd302cdd4285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R87e2d3ab65834cf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R9ef0ff9e3a134db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R6dba966ea766449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R3f41c9387d314e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R26657b84fd4f4923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R037ea2dda2874c1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R14ec58d6958249c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R9a1ed5db2001480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rb3d3594524434cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R891415343bc24136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R03c1f2d088054a5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R1fe1b3a175fb46cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R985fd4d5ea984b88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Rf28079ed649d4209"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="R72d39e458bf941be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R80ae21d801f94872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="Rfe88b93e9a094869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R211f56b9dc354f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0045" sheetId="24" r:id="R65eb048b2a1e45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0046" sheetId="25" r:id="R1e4cd00af5424f78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0047" sheetId="26" r:id="R2e47541beb1a4432"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0048" sheetId="27" r:id="R32e6994f68c24989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0049" sheetId="28" r:id="Ra1eec990d01f4482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0050" sheetId="29" r:id="R09722452557143da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0051" sheetId="30" r:id="R33726da3d2624ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0052" sheetId="31" r:id="Rd2d1ff8dd3344a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0053" sheetId="32" r:id="R850e8acddb9a405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0054" sheetId="33" r:id="Rdf733fc99f3f4b96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0055" sheetId="34" r:id="R592501e24cc447a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0056" sheetId="35" r:id="R0f72ded6b3964b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0057" sheetId="36" r:id="R3a4a53f3e18b41f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0058" sheetId="37" r:id="R5dced295e31b4fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0059" sheetId="38" r:id="Rbe725aa1217045b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0060" sheetId="39" r:id="Rfbaf628e6d9d46f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0061" sheetId="40" r:id="Rf1a3f1e137f24965"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0062" sheetId="41" r:id="Rdfa55ee317d4488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0063" sheetId="42" r:id="R5347a00455d543f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0064" sheetId="43" r:id="Rb1e6922bbe9146b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0065" sheetId="44" r:id="R463a6d6d077249c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0066" sheetId="45" r:id="R1c938267096d4714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0067" sheetId="46" r:id="R1ecf1e5df7d949dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0068" sheetId="47" r:id="R780e370930cc495a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0069" sheetId="48" r:id="R013b60d98e8043c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0070" sheetId="49" r:id="R8ccd451b708c4251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0071" sheetId="50" r:id="R42d54da3b4c24371"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0072" sheetId="51" r:id="R0a92bd5065664c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0073" sheetId="52" r:id="R4278bd94c7774b91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0074" sheetId="53" r:id="R9b746240389547d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0075" sheetId="54" r:id="Rd3781abfdc61491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0076" sheetId="55" r:id="R4d60abfe9ca642ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0077" sheetId="56" r:id="R8db564fe20214d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0078" sheetId="57" r:id="Ra5900e18e0f14d29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0079" sheetId="58" r:id="R51e220fd7a524202"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0080" sheetId="59" r:id="R5745dadd1ad94b04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0081" sheetId="60" r:id="R93b03fb08c314857"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0082" sheetId="61" r:id="R98d2089635154d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0083" sheetId="62" r:id="Ra60286845e394d50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0084" sheetId="63" r:id="Ra249c48a0ca14021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0085" sheetId="64" r:id="R96c556f451f34de1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Directory" sheetId="65" r:id="Ra4ccae54b484419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0086" sheetId="66" r:id="R437c855ed62f4840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0087" sheetId="67" r:id="R895fd27b6c6c472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0088" sheetId="68" r:id="Ref6aee4c4a3d44e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0089" sheetId="69" r:id="Rde1aaf992ade4566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0090" sheetId="70" r:id="R0a5411202e8e4315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0091" sheetId="71" r:id="R3148ee128fe24535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0092" sheetId="72" r:id="R1a1703e51eb44876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0093" sheetId="73" r:id="R121545e7c1da4d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0094" sheetId="74" r:id="R6ecff32f3a334345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0095" sheetId="75" r:id="R4a66e38b94614ed6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0096" sheetId="76" r:id="R0aa6c548e5d84c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0097" sheetId="77" r:id="R8a49625cfcb44983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0098" sheetId="78" r:id="Rc2d042b5d61e49b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0099" sheetId="79" r:id="R7093d5b593314570"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0100" sheetId="80" r:id="R69b40280e2e745fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0101" sheetId="81" r:id="R89342e2d166f4630"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0102" sheetId="82" r:id="Rbe94ce36bf0b4c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0103" sheetId="83" r:id="R352f17a560dd476f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0104" sheetId="84" r:id="Rfd431743ac5c41a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0105" sheetId="85" r:id="Rc934d7c0b2c142c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -93,7 +97,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -116,6 +120,12 @@
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -136,7 +146,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -147,6 +157,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -465,7 +476,7 @@
         <x:v>Total COA Records</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>Synced from COA Database</x:v>
@@ -491,7 +502,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>99.595</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="C5" t="str">
         <x:v>Populated purity results</x:v>
@@ -504,7 +515,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6"/>
       <x:c r="D6"/>
@@ -550,7 +561,7 @@
         <x:v>Latest COA Date</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-27</x:v>
       </x:c>
       <x:c r="C10"/>
       <x:c r="D10"/>
@@ -1069,7 +1080,7 @@
         <x:v>Total COA/Test Records</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>All records from COA Database</x:v>
@@ -1150,7 +1161,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" t="str">
         <x:v>Status column</x:v>
@@ -1231,7 +1242,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B9" t="n">
-        <x:v>99.595</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>Based on populated purity values</x:v>
@@ -1285,7 +1296,7 @@
         <x:v>Last Test Date</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-27</x:v>
       </x:c>
       <x:c r="C11" t="str">
         <x:v>Most recent test date</x:v>
@@ -7320,6 +7331,242 @@
         <x:v>Reported 2026-10-14. BPC-157 acetate; HPLC VWD SOP-043: potency 24.36%, 243.62mg/g, 19.66mg/unit. Expanded uncertainty +/-7.81% at 95% confidence. No sterility or endotoxin results supplied.</x:v>
       </x:c>
     </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D115" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E115" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F115" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G115" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H115" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="L115" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="N115" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="O115" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P115" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q115" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="R115" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S115" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D116" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E116" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F116" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G116" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H116" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="L116" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="N116" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="O116" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P116" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q116" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R116" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S116" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D117" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E117" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F117" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G117" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H117" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="L117" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="N117" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="O117" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P117" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q117" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R117" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S117" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D118" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E118" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F118" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G118" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H118" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="L118" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="N118" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="O118" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P118" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q118" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R118" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S118" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -18770,6 +19017,278 @@
       </x:c>
       <x:c r="V102" t="str">
         <x:v>Purple cap / silver crimp visible or listed in supplied report.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="V103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -20508,43 +21027,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>COA-0005</x:v>
+        <x:v>COA-0102</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>11.77</x:v>
+        <x:v>113.38</x:v>
       </x:c>
       <x:c r="G4" t="n">
-        <x:v>0.177</x:v>
+        <x:v>0.1338</x:v>
       </x:c>
       <x:c r="H4" t="n">
-        <x:v>99.963</x:v>
+        <x:v>99.99</x:v>
       </x:c>
       <x:c r="I4" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K4" t="n">
-        <x:v>46117</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L4" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Light Blue</x:v>
       </x:c>
       <x:c r="M4" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>Trivial-3R / Retatrutide; batch avg</x:v>
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -20552,43 +21071,43 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>COA-0019</x:v>
+        <x:v>COA-0103</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Cellular Support</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>10</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>8.88</x:v>
+        <x:v>1054.63</x:v>
       </x:c>
       <x:c r="G5" t="n">
-        <x:v>-0.1119999999999999</x:v>
+        <x:v>0.054630000000000005</x:v>
       </x:c>
       <x:c r="H5" t="n">
-        <x:v>99.95</x:v>
+        <x:v>99.99</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>Underfilled</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K5" t="n">
-        <x:v>46155</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L5" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>White</x:v>
       </x:c>
       <x:c r="M5" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N5" t="str">
-        <x:v>Elamipretide; tested twice</x:v>
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -20596,34 +21115,34 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>COA-0063</x:v>
+        <x:v>COA-0005</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>5-Amino-1MQ</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>Metabolic / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" t="n">
-        <x:v>5.27</x:v>
+        <x:v>11.77</x:v>
       </x:c>
       <x:c r="G6" t="n">
-        <x:v>0.053999999999999916</x:v>
+        <x:v>0.177</x:v>
       </x:c>
       <x:c r="H6" t="n">
-        <x:v>99.93</x:v>
+        <x:v>99.963</x:v>
       </x:c>
       <x:c r="I6" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>08/29/2026</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:v>46117</x:v>
       </x:c>
       <x:c r="L6" t="str">
         <x:v>Not Listed</x:v>
@@ -20632,7 +21151,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.93%; net content 5.27 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GJA8JYCE.</x:v>
+        <x:v>Trivial-3R / Retatrutide; batch avg</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -20640,43 +21159,43 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>COA-0027</x:v>
+        <x:v>COA-0019</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>ADAMAX</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>Research Peptide</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>10.92</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="G7" t="n">
-        <x:v>0.092</x:v>
+        <x:v>-0.1119999999999999</x:v>
       </x:c>
       <x:c r="H7" t="n">
-        <x:v>99.91</x:v>
+        <x:v>99.95</x:v>
       </x:c>
       <x:c r="I7" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K7" t="n">
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="L7" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M7" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>Adamax 10mg with heavy metal and endotoxin screen</x:v>
+        <x:v>Elamipretide; tested twice</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -20684,43 +21203,43 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>COA-0055</x:v>
+        <x:v>COA-0063</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>5-Amino-1MQ</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Research</x:v>
       </x:c>
       <x:c r="E8" t="n">
-        <x:v>40</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>43.16</x:v>
+        <x:v>5.27</x:v>
       </x:c>
       <x:c r="G8" t="n">
-        <x:v>0.079</x:v>
+        <x:v>0.053999999999999916</x:v>
       </x:c>
       <x:c r="H8" t="n">
-        <x:v>99.9</x:v>
+        <x:v>99.93</x:v>
       </x:c>
       <x:c r="I8" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>08/29/2026</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>Clear Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M8" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.93%; net content 5.27 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GJA8JYCE.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -20728,43 +21247,43 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>COA-0085</x:v>
+        <x:v>COA-0027</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>ADAMAX</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Research Peptide</x:v>
       </x:c>
       <x:c r="E9" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>41.14</x:v>
+        <x:v>10.92</x:v>
       </x:c>
       <x:c r="G9" t="n">
-        <x:v>0.028500000000000015</x:v>
+        <x:v>0.092</x:v>
       </x:c>
       <x:c r="H9" t="n">
-        <x:v>99.9</x:v>
+        <x:v>99.91</x:v>
       </x:c>
       <x:c r="I9" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="L9" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.9%; net content 41.14 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code UYWCCYSG.</x:v>
+        <x:v>Adamax 10mg with heavy metal and endotoxin screen</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -20772,22 +21291,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>COA-0097</x:v>
+        <x:v>COA-0085</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>Metabolic / Mitochondrial</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E10" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>9.5</x:v>
+        <x:v>41.14</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>-0.05</x:v>
+        <x:v>0.028500000000000015</x:v>
       </x:c>
       <x:c r="H10" t="n">
         <x:v>99.9</x:v>
@@ -20796,19 +21315,19 @@
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>BTLabs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L10" t="str">
-        <x:v>Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Issued 2026-08-26. HPLC potency 9.5mg (94.6% as printed). Gross powder mass 124.2mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.9%; net content 41.14 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code UYWCCYSG.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -20816,43 +21335,43 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>COA-0021</x:v>
+        <x:v>COA-0055</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E11" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>9.66</x:v>
+        <x:v>43.16</x:v>
       </x:c>
       <x:c r="G11" t="n">
-        <x:v>-0.03399999999999999</x:v>
+        <x:v>0.079</x:v>
       </x:c>
       <x:c r="H11" t="n">
-        <x:v>99.897</x:v>
+        <x:v>99.9</x:v>
       </x:c>
       <x:c r="I11" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K11" t="n">
-        <x:v>46156</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear Purple</x:v>
       </x:c>
       <x:c r="M11" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Mod GRF 1-29</x:v>
+        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -20860,43 +21379,43 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>COA-0012</x:v>
+        <x:v>COA-0097</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Metabolic / Mitochondrial</x:v>
       </x:c>
       <x:c r="E12" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F12" t="n">
-        <x:v>5.95</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="G12" t="n">
-        <x:v>0.19</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="H12" t="n">
-        <x:v>99.883</x:v>
+        <x:v>99.9</x:v>
       </x:c>
       <x:c r="I12" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K12" t="n">
-        <x:v>46156</x:v>
+        <x:v>BTLabs</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>rHGH fragment / AOD-9604</x:v>
+        <x:v>Issued 2026-08-26. HPLC potency 9.5mg (94.6% as printed). Gross powder mass 124.2mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -20904,43 +21423,43 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>COA-0024</x:v>
+        <x:v>COA-0021</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E13" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F13" t="n">
-        <x:v>22.47</x:v>
+        <x:v>9.66</x:v>
       </x:c>
       <x:c r="G13" t="n">
-        <x:v>0.1234999999999999</x:v>
+        <x:v>-0.03399999999999999</x:v>
       </x:c>
       <x:c r="H13" t="n">
-        <x:v>99.86</x:v>
+        <x:v>99.897</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>2026-06-14</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K13" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>Clear Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Retatrutide 20mg, separate batch from existing Retatrutide records; received 06/11/2026, reported 06/14/2026.</x:v>
+        <x:v>Mod GRF 1-29</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -20948,34 +21467,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>COA-0057</x:v>
+        <x:v>COA-0012</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Fat Loss</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F14" t="n">
-        <x:v>37.37</x:v>
+        <x:v>5.95</x:v>
       </x:c>
       <x:c r="G14" t="n">
-        <x:v>0.24566666666666667</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="H14" t="n">
-        <x:v>99.86</x:v>
+        <x:v>99.883</x:v>
       </x:c>
       <x:c r="I14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Pristin Biotech</x:v>
-      </x:c>
-      <x:c r="K14" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K14" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L14" t="str">
         <x:v>Not Listed</x:v>
@@ -20984,7 +21503,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
+        <x:v>rHGH fragment / AOD-9604</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -20992,34 +21511,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>COA-0069</x:v>
+        <x:v>COA-0057</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>Cosmetic / Skin Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>52.21</x:v>
+        <x:v>37.37</x:v>
       </x:c>
       <x:c r="G15" t="n">
-        <x:v>0.04420000000000002</x:v>
+        <x:v>0.24566666666666667</x:v>
       </x:c>
       <x:c r="H15" t="n">
-        <x:v>99.85</x:v>
+        <x:v>99.86</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Pristin Biotech</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L15" t="str">
         <x:v>Not Listed</x:v>
@@ -21028,7 +21547,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.85%; net content 52.21 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 3SDBWEB6.</x:v>
+        <x:v>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -21036,43 +21555,43 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>COA-0093</x:v>
+        <x:v>COA-0024</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F16" t="n">
-        <x:v>10.14</x:v>
+        <x:v>22.47</x:v>
       </x:c>
       <x:c r="G16" t="n">
-        <x:v>0.014000000000000002</x:v>
+        <x:v>0.1234999999999999</x:v>
       </x:c>
       <x:c r="H16" t="n">
-        <x:v>99.85</x:v>
+        <x:v>99.86</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>PurePoint Analytical</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>2026-10-01</x:v>
+        <x:v>2026-06-14</x:v>
       </x:c>
       <x:c r="L16" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Clear Green</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Issued 2026-10-02. Identity confirmed by LC-MS; HPLC/UV purity and net content passed.</x:v>
+        <x:v>Retatrutide 20mg, separate batch from existing Retatrutide records; received 06/11/2026, reported 06/14/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -21080,43 +21599,43 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>COA-0050</x:v>
+        <x:v>COA-0069</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>Cosmetic / Skin Research</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>10.38</x:v>
+        <x:v>52.21</x:v>
       </x:c>
       <x:c r="G17" t="n">
-        <x:v>0.038</x:v>
+        <x:v>0.04420000000000002</x:v>
       </x:c>
       <x:c r="H17" t="n">
-        <x:v>99.849</x:v>
+        <x:v>99.85</x:v>
       </x:c>
       <x:c r="I17" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K17" t="n">
-        <x:v>46242</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L17" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.85%; net content 52.21 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 3SDBWEB6.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -21124,43 +21643,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>COA-0013</x:v>
+        <x:v>COA-0093</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E18" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F18" t="n">
-        <x:v>10.58</x:v>
+        <x:v>10.14</x:v>
       </x:c>
       <x:c r="G18" t="n">
-        <x:v>0.05800000000000001</x:v>
+        <x:v>0.014000000000000002</x:v>
       </x:c>
       <x:c r="H18" t="n">
-        <x:v>99.847</x:v>
+        <x:v>99.85</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K18" t="n">
-        <x:v>46057</x:v>
+        <x:v>PurePoint Analytical</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>2026-10-01</x:v>
       </x:c>
       <x:c r="L18" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>10 mg label</x:v>
+        <x:v>Issued 2026-10-02. Identity confirmed by LC-MS; HPLC/UV purity and net content passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -21168,43 +21687,43 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>COA-0010</x:v>
+        <x:v>COA-0050</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E19" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" t="n">
-        <x:v>32.5</x:v>
+        <x:v>10.38</x:v>
       </x:c>
       <x:c r="G19" t="n">
-        <x:v>0.08333333333333333</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="H19" t="n">
-        <x:v>99.84</x:v>
+        <x:v>99.849</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K19" t="n">
-        <x:v>46059</x:v>
+        <x:v>46242</x:v>
       </x:c>
       <x:c r="L19" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>30 mg label</x:v>
+        <x:v>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -21212,34 +21731,34 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>COA-0070</x:v>
+        <x:v>COA-0013</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>GLOW</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E20" t="n">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F20" t="n">
-        <x:v>72.68</x:v>
+        <x:v>10.58</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>0.03828571428571438</x:v>
+        <x:v>0.05800000000000001</x:v>
       </x:c>
       <x:c r="H20" t="n">
-        <x:v>99.84</x:v>
+        <x:v>99.847</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K20" t="str">
-        <x:v>08/28/2026</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K20" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>Not Listed</x:v>
@@ -21248,7 +21767,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.84%; net content 72.68 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code CAB37LKM.</x:v>
+        <x:v>10 mg label</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -21256,34 +21775,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>COA-0058</x:v>
+        <x:v>COA-0070</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>GLOW</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E21" t="n">
-        <x:v>10</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F21" t="n">
-        <x:v>10.8</x:v>
+        <x:v>72.68</x:v>
       </x:c>
       <x:c r="G21" t="n">
-        <x:v>0.08</x:v>
+        <x:v>0.03828571428571438</x:v>
       </x:c>
       <x:c r="H21" t="n">
-        <x:v>99.83</x:v>
+        <x:v>99.84</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Pristin Biotech</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>08/28/2026</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>Not Listed</x:v>
@@ -21292,7 +21811,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.84%; net content 72.68 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code CAB37LKM.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -21300,10 +21819,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>COA-0022</x:v>
+        <x:v>COA-0010</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>GLP-1 / Weight</x:v>
@@ -21312,13 +21831,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F22" t="n">
-        <x:v>34.77</x:v>
+        <x:v>32.5</x:v>
       </x:c>
       <x:c r="G22" t="n">
-        <x:v>0.1590000000000001</x:v>
+        <x:v>0.08333333333333333</x:v>
       </x:c>
       <x:c r="H22" t="n">
-        <x:v>99.825</x:v>
+        <x:v>99.84</x:v>
       </x:c>
       <x:c r="I22" t="str">
         <x:v>Overfilled</x:v>
@@ -21327,7 +21846,7 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K22" t="n">
-        <x:v>46156</x:v>
+        <x:v>46059</x:v>
       </x:c>
       <x:c r="L22" t="str">
         <x:v>Not Listed</x:v>
@@ -21336,7 +21855,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</x:v>
+        <x:v>30 mg label</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -21344,43 +21863,43 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>COA-0036</x:v>
+        <x:v>COA-0058</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>KLOW 80mg</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E23" t="n">
-        <x:v>80</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F23" t="n">
-        <x:v>96.46</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="G23" t="n">
-        <x:v>0.20575000000000002</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="H23" t="n">
-        <x:v>99.82</x:v>
+        <x:v>99.83</x:v>
       </x:c>
       <x:c r="I23" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Pristin Biotech</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
+        <x:v>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -21388,43 +21907,43 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>COA-0090</x:v>
+        <x:v>COA-0022</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E24" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>58.95</x:v>
+        <x:v>34.77</x:v>
       </x:c>
       <x:c r="G24" t="n">
-        <x:v>0.179</x:v>
+        <x:v>0.1590000000000001</x:v>
       </x:c>
       <x:c r="H24" t="n">
-        <x:v>99.82</x:v>
+        <x:v>99.825</x:v>
       </x:c>
       <x:c r="I24" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K24" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K24" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.82%; net content 58.95 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.84% / 59.02 mg and 99.79% / 58.88 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -21432,43 +21951,43 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>COA-0015</x:v>
+        <x:v>COA-0090</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E25" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F25" t="n">
-        <x:v>38.96</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="G25" t="n">
-        <x:v>-0.02599999999999998</x:v>
+        <x:v>0.179</x:v>
       </x:c>
       <x:c r="H25" t="n">
-        <x:v>99.813</x:v>
+        <x:v>99.82</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K25" t="n">
-        <x:v>46057</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>40 mg label</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.82%; net content 58.95 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.84% / 59.02 mg and 99.79% / 58.88 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -21476,43 +21995,43 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>COA-0028</x:v>
+        <x:v>COA-0036</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>BPC/TB Blend</x:v>
+        <x:v>KLOW 80mg</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E26" t="n">
-        <x:v>10</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F26" t="n">
-        <x:v>11.85</x:v>
+        <x:v>96.46</x:v>
       </x:c>
       <x:c r="G26" t="n">
-        <x:v>0.185</x:v>
+        <x:v>0.20575000000000002</x:v>
       </x:c>
       <x:c r="H26" t="n">
-        <x:v>99.81</x:v>
+        <x:v>99.82</x:v>
       </x:c>
       <x:c r="I26" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -21520,43 +22039,43 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>COA-0009</x:v>
+        <x:v>COA-0015</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E27" t="n">
-        <x:v>60</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F27" t="n">
-        <x:v>65.1</x:v>
+        <x:v>38.96</x:v>
       </x:c>
       <x:c r="G27" t="n">
-        <x:v>0.08499999999999991</x:v>
+        <x:v>-0.02599999999999998</x:v>
       </x:c>
       <x:c r="H27" t="n">
-        <x:v>99.8</x:v>
+        <x:v>99.813</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>BT Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K27" t="n">
-        <x:v>46133</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>Gold</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M27" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>60 mg label; 108.5% potency</x:v>
+        <x:v>40 mg label</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -21564,34 +22083,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>COA-0056</x:v>
+        <x:v>COA-0028</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Tesamorelin</x:v>
+        <x:v>BPC/TB Blend</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E28" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F28" t="n">
-        <x:v>12.18</x:v>
+        <x:v>11.85</x:v>
       </x:c>
       <x:c r="G28" t="n">
-        <x:v>0.21800000000000003</x:v>
+        <x:v>0.185</x:v>
       </x:c>
       <x:c r="H28" t="n">
-        <x:v>99.79</x:v>
+        <x:v>99.81</x:v>
       </x:c>
       <x:c r="I28" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>Pristin Biotech</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L28" t="str">
         <x:v>Not Listed</x:v>
@@ -21600,7 +22119,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
+        <x:v>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -21608,43 +22127,43 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>COA-0071</x:v>
+        <x:v>COA-0009</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>KLOW</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E29" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F29" t="n">
-        <x:v>82.72</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="G29" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.08499999999999991</x:v>
       </x:c>
       <x:c r="H29" t="n">
-        <x:v>99.79</x:v>
+        <x:v>99.8</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K29" t="str">
-        <x:v>08/28/2026</x:v>
+        <x:v>BT Labs</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Gold</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.79%; net content 82.72 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GRD4V5KA.</x:v>
+        <x:v>60 mg label; 108.5% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -21652,22 +22171,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>COA-0078</x:v>
+        <x:v>COA-0087</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Healing / Anti-Inflammatory Research</x:v>
       </x:c>
       <x:c r="E30" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>21.38</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="G30" t="n">
-        <x:v>0.06899999999999995</x:v>
+        <x:v>0.304</x:v>
       </x:c>
       <x:c r="H30" t="n">
         <x:v>99.79</x:v>
@@ -21676,19 +22195,19 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M30" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.79%; net content 21.38 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6V3BNXVB.</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.79%; net content 13.04 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.78% / 13.21 mg and 99.80% / 12.87 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -21696,22 +22215,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>COA-0087</x:v>
+        <x:v>COA-0078</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>Healing / Anti-Inflammatory Research</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E31" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F31" t="n">
-        <x:v>13.04</x:v>
+        <x:v>21.38</x:v>
       </x:c>
       <x:c r="G31" t="n">
-        <x:v>0.304</x:v>
+        <x:v>0.06899999999999995</x:v>
       </x:c>
       <x:c r="H31" t="n">
         <x:v>99.79</x:v>
@@ -21720,19 +22239,19 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M31" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.79%; net content 13.04 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.78% / 13.21 mg and 99.80% / 12.87 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.79%; net content 21.38 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6V3BNXVB.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -21740,43 +22259,43 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>COA-0041</x:v>
+        <x:v>COA-0071</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>KLOW</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>Cosmetic / Recovery</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E32" t="n">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F32" t="n">
-        <x:v>51.34</x:v>
+        <x:v>82.72</x:v>
       </x:c>
       <x:c r="G32" t="n">
-        <x:v>0.026800000000000067</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H32" t="n">
-        <x:v>99.78</x:v>
+        <x:v>99.79</x:v>
       </x:c>
       <x:c r="I32" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K32" t="n">
-        <x:v>46239</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>08/28/2026</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M32" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.79%; net content 82.72 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GRD4V5KA.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -21784,34 +22303,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>COA-0068</x:v>
+        <x:v>COA-0056</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>CJC-1295 / Ipamorelin</x:v>
+        <x:v>Tesamorelin</x:v>
       </x:c>
       <x:c r="D33" t="str">
-        <x:v>Growth Hormone Support Blend</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E33" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F33" t="n">
-        <x:v>10.47</x:v>
+        <x:v>12.18</x:v>
       </x:c>
       <x:c r="G33" t="n">
-        <x:v>0.04700000000000006</x:v>
+        <x:v>0.21800000000000003</x:v>
       </x:c>
       <x:c r="H33" t="n">
-        <x:v>99.78</x:v>
+        <x:v>99.79</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Pristin Biotech</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L33" t="str">
         <x:v>Not Listed</x:v>
@@ -21820,7 +22339,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.78%; net content 10.47 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code VRDU58EW.</x:v>
+        <x:v>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -21828,43 +22347,43 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>COA-0035</x:v>
+        <x:v>COA-0068</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>CJC-1295 / Ipamorelin</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>Regenerative / Skin</x:v>
+        <x:v>Growth Hormone Support Blend</x:v>
       </x:c>
       <x:c r="E34" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F34" t="n">
-        <x:v>50.75</x:v>
+        <x:v>10.47</x:v>
       </x:c>
       <x:c r="G34" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.04700000000000006</x:v>
       </x:c>
       <x:c r="H34" t="n">
-        <x:v>99.77</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="I34" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Clear/Transparent</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M34" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.78%; net content 10.47 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code VRDU58EW.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -21872,43 +22391,43 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>COA-0034</x:v>
+        <x:v>COA-0041</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D35" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E35" t="n">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F35" t="n">
-        <x:v>15.59</x:v>
+        <x:v>51.34</x:v>
       </x:c>
       <x:c r="G35" t="n">
-        <x:v>0.03933333333333333</x:v>
+        <x:v>0.026800000000000067</x:v>
       </x:c>
       <x:c r="H35" t="n">
-        <x:v>99.747</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K35" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K35" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -21916,43 +22435,43 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>COA-0088</x:v>
+        <x:v>COA-0035</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>Regenerative / Skin</x:v>
       </x:c>
       <x:c r="E36" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F36" t="n">
-        <x:v>22.84</x:v>
+        <x:v>50.75</x:v>
       </x:c>
       <x:c r="G36" t="n">
-        <x:v>0.142</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="H36" t="n">
-        <x:v>99.74</x:v>
+        <x:v>99.77</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>Black</x:v>
+        <x:v>Clear/Transparent</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.74%; net content 22.84 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.73% / 22.96 mg and 99.75% / 22.71 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -21960,43 +22479,43 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>COA-0089</x:v>
+        <x:v>COA-0034</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D37" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E37" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F37" t="n">
-        <x:v>11.76</x:v>
+        <x:v>15.59</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>0.176</x:v>
+        <x:v>0.03933333333333333</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>99.74</x:v>
+        <x:v>99.747</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>Copper</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>Identity confirmed as GLP-RT by LC-MS; HPLC-UV purity 99.74%; net content 11.76 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.75% / 11.49 mg and 99.72% / 12.03 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -22004,43 +22523,43 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0089</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E38" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F38" t="n">
-        <x:v>16.18</x:v>
+        <x:v>11.76</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>0.07866666666666665</x:v>
+        <x:v>0.176</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.74</x:v>
       </x:c>
       <x:c r="I38" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K38" t="n">
-        <x:v>46156</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M38" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
+        <x:v>Identity confirmed as GLP-RT by LC-MS; HPLC-UV purity 99.74%; net content 11.76 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.75% / 11.49 mg and 99.72% / 12.03 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -22048,43 +22567,43 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>COA-0092</x:v>
+        <x:v>COA-0088</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D39" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E39" t="n">
-        <x:v>60</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F39" t="n">
-        <x:v>63.89</x:v>
+        <x:v>22.84</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>0.06483333333333334</x:v>
+        <x:v>0.142</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>99.727</x:v>
+        <x:v>99.74</x:v>
       </x:c>
       <x:c r="I39" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M39" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.727%; batch average net content 63.89 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.676% / 63.96 mg and 99.777% / 63.81 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.74%; net content 22.84 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.73% / 22.96 mg and 99.75% / 22.71 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -22092,34 +22611,34 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>COA-0045</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>CJC-1295</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>GHRH analog</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E40" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F40" t="n">
-        <x:v>10.52</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="G40" t="n">
-        <x:v>0.051999999999999956</x:v>
+        <x:v>0.07866666666666665</x:v>
       </x:c>
       <x:c r="H40" t="n">
-        <x:v>99.72</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="I40" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J40" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K40" t="n">
-        <x:v>46234</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L40" t="str">
         <x:v>Not Listed</x:v>
@@ -22128,7 +22647,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -22136,43 +22655,43 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>COA-0054</x:v>
+        <x:v>COA-0092</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D41" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E41" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F41" t="n">
-        <x:v>21.94</x:v>
+        <x:v>63.89</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.06483333333333334</x:v>
       </x:c>
       <x:c r="H41" t="n">
-        <x:v>99.72</x:v>
+        <x:v>99.727</x:v>
       </x:c>
       <x:c r="I41" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Clear Pink</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</x:v>
+        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.727%; batch average net content 63.89 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.676% / 63.96 mg and 99.777% / 63.81 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -22224,43 +22743,43 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>COA-0075</x:v>
+        <x:v>COA-0054</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Melanotan II</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D43" t="str">
-        <x:v>Pigmentation / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E43" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F43" t="n">
-        <x:v>10.34</x:v>
+        <x:v>21.94</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>99.71</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J43" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="L43" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear Pink</x:v>
       </x:c>
       <x:c r="M43" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N43" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.71%; net content 10.34 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code YL6Z7HBG.</x:v>
+        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -22268,25 +22787,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>COA-0084</x:v>
+        <x:v>COA-0045</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>GHRH analog</x:v>
       </x:c>
       <x:c r="E44" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F44" t="n">
-        <x:v>21.1</x:v>
+        <x:v>10.52</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>0.05500000000000007</x:v>
+        <x:v>0.051999999999999956</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>99.71</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="I44" t="str">
         <x:v>Overfilled</x:v>
@@ -22294,8 +22813,8 @@
       <x:c r="J44" t="str">
         <x:v>ILS Labs</x:v>
       </x:c>
-      <x:c r="K44" t="str">
-        <x:v>08/17/2026</x:v>
+      <x:c r="K44" t="n">
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L44" t="str">
         <x:v>Not Listed</x:v>
@@ -22304,7 +22823,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.71%; net content 21.1 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code AGBSBU2E.</x:v>
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -22312,43 +22831,43 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>COA-0007</x:v>
+        <x:v>COA-0084</x:v>
       </x:c>
       <x:c r="C45" t="str">
         <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D45" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E45" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F45" t="n">
-        <x:v>26</x:v>
+        <x:v>21.1</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.05500000000000007</x:v>
       </x:c>
       <x:c r="H45" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.71</x:v>
       </x:c>
       <x:c r="I45" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J45" t="str">
-        <x:v>BT Labs</x:v>
-      </x:c>
-      <x:c r="K45" t="n">
-        <x:v>46133</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M45" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N45" t="str">
-        <x:v>20 mg label; 130.1% potency</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.71%; net content 21.1 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code AGBSBU2E.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -22356,43 +22875,43 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>COA-0008</x:v>
+        <x:v>COA-0075</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Melanotan II</x:v>
       </x:c>
       <x:c r="D46" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Pigmentation / Research</x:v>
       </x:c>
       <x:c r="E46" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F46" t="n">
-        <x:v>46.6</x:v>
+        <x:v>10.34</x:v>
       </x:c>
       <x:c r="G46" t="n">
-        <x:v>0.165</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H46" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.71</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J46" t="str">
-        <x:v>BT Labs</x:v>
-      </x:c>
-      <x:c r="K46" t="n">
-        <x:v>46106</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L46" t="str">
-        <x:v>Gray</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M46" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N46" t="str">
-        <x:v>40 mg label; 116.4% potency</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.71%; net content 10.34 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code YL6Z7HBG.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -22444,22 +22963,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>COA-0096</x:v>
+        <x:v>COA-0008</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>KLOW</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D48" t="str">
-        <x:v>Recovery / Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E48" t="n">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F48" t="n">
-        <x:v>87.5</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="G48" t="n">
-        <x:v>0.09375</x:v>
+        <x:v>0.165</x:v>
       </x:c>
       <x:c r="H48" t="n">
         <x:v>99.7</x:v>
@@ -22468,19 +22987,19 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J48" t="str">
-        <x:v>BTLabs</x:v>
-      </x:c>
-      <x:c r="K48" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>BT Labs</x:v>
+      </x:c>
+      <x:c r="K48" t="n">
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Gray</x:v>
       </x:c>
       <x:c r="M48" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N48" t="str">
-        <x:v>Issued 2026-08-26. Components GHK-Cu 54.8mg, KPV 10.5mg, BPC-157 10.2mg, TB-500 12mg; total peptide 87.5mg. Gross powder mass 197.4mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
+        <x:v>40 mg label; 116.4% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -22488,43 +23007,43 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>COA-0094</x:v>
+        <x:v>COA-0007</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D49" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E49" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F49" t="n">
-        <x:v>9.99</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G49" t="n">
-        <x:v>-0.001</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H49" t="n">
-        <x:v>99.69</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J49" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K49" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>BT Labs</x:v>
+      </x:c>
+      <x:c r="K49" t="n">
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>Green</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="M49" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N49" t="str">
-        <x:v>Blend is CJC-1295 No DAC 5mg + Ipamorelin 5mg. Mean content: CJC 4.91mg + Ipamorelin 5.08mg. Samples: purity 99.66% / 99.72%; component contents 5.00 + 5.17mg / 4.82 + 5.00mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
+        <x:v>20 mg label; 130.1% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -22532,43 +23051,43 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>COA-0044</x:v>
+        <x:v>COA-0096</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>KLOW</x:v>
       </x:c>
       <x:c r="D50" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>Recovery / Blend</x:v>
       </x:c>
       <x:c r="E50" t="n">
-        <x:v>5</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F50" t="n">
-        <x:v>4.63</x:v>
+        <x:v>87.5</x:v>
       </x:c>
       <x:c r="G50" t="n">
-        <x:v>-0.07400000000000002</x:v>
+        <x:v>0.09375</x:v>
       </x:c>
       <x:c r="H50" t="n">
-        <x:v>99.67</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>Underfilled</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
-      </x:c>
-      <x:c r="K50" t="n">
-        <x:v>46234</x:v>
+        <x:v>BTLabs</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="L50" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M50" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N50" t="str">
-        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+        <x:v>Issued 2026-08-26. Components GHK-Cu 54.8mg, KPV 10.5mg, BPC-157 10.2mg, TB-500 12mg; total peptide 87.5mg. Gross powder mass 197.4mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -22576,43 +23095,43 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0094</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
       </x:c>
       <x:c r="D51" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E51" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F51" t="n">
-        <x:v>6.63</x:v>
+        <x:v>9.99</x:v>
       </x:c>
       <x:c r="G51" t="n">
-        <x:v>0.326</x:v>
+        <x:v>-0.001</x:v>
       </x:c>
       <x:c r="H51" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.69</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K51" t="n">
-        <x:v>46174</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K51" t="str">
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="L51" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M51" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N51" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Blend is CJC-1295 No DAC 5mg + Ipamorelin 5mg. Mean content: CJC 4.91mg + Ipamorelin 5.08mg. Samples: purity 99.66% / 99.72%; component contents 5.00 + 5.17mg / 4.82 + 5.00mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -22620,43 +23139,43 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="D52" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E52" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F52" t="n">
-        <x:v>15.53</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="G52" t="n">
-        <x:v>0.035333333333333335</x:v>
+        <x:v>-0.07400000000000002</x:v>
       </x:c>
       <x:c r="H52" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>On label</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K52" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L52" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M52" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N52" t="str">
-        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -22664,25 +23183,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D53" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E53" t="n">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F53" t="n">
-        <x:v>33.24</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="G53" t="n">
-        <x:v>0.10800000000000001</x:v>
+        <x:v>0.326</x:v>
       </x:c>
       <x:c r="H53" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="I53" t="str">
         <x:v>Overfilled</x:v>
@@ -22690,17 +23209,17 @@
       <x:c r="J53" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K53" t="str">
-        <x:v>2026-07-03</x:v>
+      <x:c r="K53" t="n">
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="L53" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M53" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N53" t="str">
-        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -22708,43 +23227,43 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>COA-0047</x:v>
+        <x:v>COA-0032</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D54" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E54" t="n">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F54" t="n">
-        <x:v>63.37</x:v>
+        <x:v>15.53</x:v>
       </x:c>
       <x:c r="G54" t="n">
-        <x:v>0.05616666666666662</x:v>
+        <x:v>0.035333333333333335</x:v>
       </x:c>
       <x:c r="H54" t="n">
-        <x:v>99.59</x:v>
+        <x:v>99.642</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>Red</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M54" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N54" t="str">
-        <x:v>Identity confirmed as Retatrutide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -22752,43 +23271,43 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>COA-0020</x:v>
+        <x:v>COA-0033</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D55" t="str">
-        <x:v>Other</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E55" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F55" t="n">
-        <x:v>12.19</x:v>
+        <x:v>33.24</x:v>
       </x:c>
       <x:c r="G55" t="n">
-        <x:v>0.2189999999999999</x:v>
+        <x:v>0.10800000000000001</x:v>
       </x:c>
       <x:c r="H55" t="n">
-        <x:v>99.589</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="I55" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J55" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K55" t="n">
-        <x:v>46057</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K55" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L55" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M55" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N55" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -22796,7 +23315,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0047</x:v>
       </x:c>
       <x:c r="C56" t="str">
         <x:v>Retatrutide</x:v>
@@ -22805,34 +23324,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E56" t="n">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F56" t="n">
-        <x:v>33.77</x:v>
+        <x:v>63.37</x:v>
       </x:c>
       <x:c r="G56" t="n">
-        <x:v>0.12566666666666668</x:v>
+        <x:v>0.05616666666666662</x:v>
       </x:c>
       <x:c r="H56" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.59</x:v>
       </x:c>
       <x:c r="I56" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J56" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M56" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N56" t="str">
-        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Identity confirmed as Retatrutide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -22840,34 +23359,34 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>COA-0081</x:v>
+        <x:v>COA-0020</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>Semax</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D57" t="str">
-        <x:v>Nootropic / Research</x:v>
+        <x:v>Other</x:v>
       </x:c>
       <x:c r="E57" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F57" t="n">
-        <x:v>10.5</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="G57" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.2189999999999999</x:v>
       </x:c>
       <x:c r="H57" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.589</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J57" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K57" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K57" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L57" t="str">
         <x:v>Not Listed</x:v>
@@ -22876,7 +23395,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N57" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.58%; net content 10.5 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6293KLTS.</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -22928,43 +23447,43 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>COA-0040</x:v>
+        <x:v>COA-0081</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>Semax</x:v>
       </x:c>
       <x:c r="D59" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Nootropic / Research</x:v>
       </x:c>
       <x:c r="E59" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F59" t="n">
-        <x:v>5.13</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="G59" t="n">
-        <x:v>0.025999999999999978</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="H59" t="n">
-        <x:v>99.57</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J59" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K59" t="n">
-        <x:v>46239</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K59" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L59" t="str">
-        <x:v>Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M59" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N59" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.58%; net content 10.5 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6293KLTS.</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -22972,34 +23491,34 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>COA-0080</x:v>
+        <x:v>COA-0031</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>Selank</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D60" t="str">
-        <x:v>Nootropic / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E60" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F60" t="n">
-        <x:v>10.66</x:v>
+        <x:v>33.77</x:v>
       </x:c>
       <x:c r="G60" t="n">
-        <x:v>0.06600000000000002</x:v>
+        <x:v>0.12566666666666668</x:v>
       </x:c>
       <x:c r="H60" t="n">
-        <x:v>99.57</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I60" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J60" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L60" t="str">
         <x:v>Not Listed</x:v>
@@ -23008,7 +23527,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N60" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.57%; net content 10.66 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code JBYELVFU.</x:v>
+        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -23016,43 +23535,43 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>COA-0026</x:v>
+        <x:v>COA-0080</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Selank</x:v>
       </x:c>
       <x:c r="D61" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Nootropic / Research</x:v>
       </x:c>
       <x:c r="E61" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F61" t="n">
-        <x:v>42.53</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G61" t="n">
-        <x:v>0.06325</x:v>
+        <x:v>0.06600000000000002</x:v>
       </x:c>
       <x:c r="H61" t="n">
-        <x:v>99.569</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I61" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J61" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L61" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M61" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N61" t="str">
-        <x:v>Blue cap Retatrutide 40mg</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.57%; net content 10.66 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code JBYELVFU.</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -23060,43 +23579,43 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>COA-0060</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>Semax</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D62" t="str">
-        <x:v>Nootropic / Research</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E62" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F62" t="n">
-        <x:v>9.65</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="G62" t="n">
-        <x:v>-0.034999999999999996</x:v>
+        <x:v>0.025999999999999978</x:v>
       </x:c>
       <x:c r="H62" t="n">
-        <x:v>99.568</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K62" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K62" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L62" t="str">
-        <x:v>Black</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M62" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N62" t="str">
-        <x:v>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -23104,7 +23623,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>COA-0025</x:v>
+        <x:v>COA-0026</x:v>
       </x:c>
       <x:c r="C63" t="str">
         <x:v>Retatrutide</x:v>
@@ -23113,16 +23632,16 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E63" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F63" t="n">
-        <x:v>33.31</x:v>
+        <x:v>42.53</x:v>
       </x:c>
       <x:c r="G63" t="n">
-        <x:v>0.1103333333333333</x:v>
+        <x:v>0.06325</x:v>
       </x:c>
       <x:c r="H63" t="n">
-        <x:v>99.563</x:v>
+        <x:v>99.569</x:v>
       </x:c>
       <x:c r="I63" t="str">
         <x:v>Overfilled</x:v>
@@ -23134,13 +23653,13 @@
         <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L63" t="str">
-        <x:v>Transparent</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M63" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N63" t="str">
-        <x:v>Transparent cap Retatrutide 30mg</x:v>
+        <x:v>Blue cap Retatrutide 40mg</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -23148,25 +23667,25 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>COA-0046</x:v>
+        <x:v>COA-0060</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>NAD+</x:v>
+        <x:v>Semax</x:v>
       </x:c>
       <x:c r="D64" t="str">
-        <x:v>Metabolic / Cellular Energy</x:v>
+        <x:v>Nootropic / Research</x:v>
       </x:c>
       <x:c r="E64" t="n">
-        <x:v>500</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F64" t="n">
-        <x:v>488.47</x:v>
+        <x:v>9.65</x:v>
       </x:c>
       <x:c r="G64" t="n">
-        <x:v>-0.023059999999999945</x:v>
+        <x:v>-0.034999999999999996</x:v>
       </x:c>
       <x:c r="H64" t="n">
-        <x:v>99.549</x:v>
+        <x:v>99.568</x:v>
       </x:c>
       <x:c r="I64" t="str">
         <x:v>On label</x:v>
@@ -23174,8 +23693,8 @@
       <x:c r="J64" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K64" t="n">
-        <x:v>46232</x:v>
+      <x:c r="K64" t="str">
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="L64" t="str">
         <x:v>Black</x:v>
@@ -23184,7 +23703,7 @@
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N64" t="str">
-        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+        <x:v>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -23192,43 +23711,43 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>COA-0079</x:v>
+        <x:v>COA-0025</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D65" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E65" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F65" t="n">
-        <x:v>10.7</x:v>
+        <x:v>33.31</x:v>
       </x:c>
       <x:c r="G65" t="n">
-        <x:v>0.06999999999999992</x:v>
+        <x:v>0.1103333333333333</x:v>
       </x:c>
       <x:c r="H65" t="n">
-        <x:v>99.53</x:v>
+        <x:v>99.563</x:v>
       </x:c>
       <x:c r="I65" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L65" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Transparent</x:v>
       </x:c>
       <x:c r="M65" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N65" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.53%; net content 10.7 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code KSU4VSE7.</x:v>
+        <x:v>Transparent cap Retatrutide 30mg</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -23236,43 +23755,43 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>COA-0038</x:v>
+        <x:v>COA-0046</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D66" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Cellular Energy</x:v>
       </x:c>
       <x:c r="E66" t="n">
-        <x:v>10</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F66" t="n">
-        <x:v>10.09</x:v>
+        <x:v>488.47</x:v>
       </x:c>
       <x:c r="G66" t="n">
-        <x:v>0.008999999999999985</x:v>
+        <x:v>-0.023059999999999945</x:v>
       </x:c>
       <x:c r="H66" t="n">
-        <x:v>99.52</x:v>
+        <x:v>99.549</x:v>
       </x:c>
       <x:c r="I66" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K66" t="n">
-        <x:v>46239</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="L66" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M66" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N66" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -23280,34 +23799,34 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0079</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D67" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E67" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F67" t="n">
-        <x:v>11.8</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="G67" t="n">
-        <x:v>0.1800000000000001</x:v>
+        <x:v>0.06999999999999992</x:v>
       </x:c>
       <x:c r="H67" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.53</x:v>
       </x:c>
       <x:c r="I67" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J67" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K67" t="n">
-        <x:v>46156</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L67" t="str">
         <x:v>Not Listed</x:v>
@@ -23316,7 +23835,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N67" t="str">
-        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.53%; net content 10.7 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code KSU4VSE7.</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -23324,43 +23843,43 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>COA-0059</x:v>
+        <x:v>COA-0038</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>Glutathione</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D68" t="str">
-        <x:v>Antioxidant / Cellular Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E68" t="n">
-        <x:v>1500</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F68" t="n">
-        <x:v>1478.47</x:v>
+        <x:v>10.09</x:v>
       </x:c>
       <x:c r="G68" t="n">
-        <x:v>-0.014353333333333334</x:v>
+        <x:v>0.008999999999999985</x:v>
       </x:c>
       <x:c r="H68" t="n">
-        <x:v>99.513</x:v>
+        <x:v>99.52</x:v>
       </x:c>
       <x:c r="I68" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J68" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K68" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K68" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L68" t="str">
-        <x:v>Red</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M68" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N68" t="str">
-        <x:v>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -23368,7 +23887,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="C69" t="str">
         <x:v>Retatrutide</x:v>
@@ -23376,22 +23895,26 @@
       <x:c r="D69" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E69"/>
+      <x:c r="E69" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F69" t="n">
-        <x:v>22.47</x:v>
-      </x:c>
-      <x:c r="G69"/>
+        <x:v>11.8</x:v>
+      </x:c>
+      <x:c r="G69" t="n">
+        <x:v>0.1800000000000001</x:v>
+      </x:c>
       <x:c r="H69" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>Review</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J69" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K69" t="n">
-        <x:v>46146</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L69" t="str">
         <x:v>Not Listed</x:v>
@@ -23400,7 +23923,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N69" t="str">
-        <x:v>Labeled quantity unclear from image</x:v>
+        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -23408,43 +23931,43 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0059</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Glutathione</x:v>
       </x:c>
       <x:c r="D70" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Antioxidant / Cellular Support</x:v>
       </x:c>
       <x:c r="E70" t="n">
-        <x:v>15</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="F70" t="n">
-        <x:v>17.93</x:v>
+        <x:v>1478.47</x:v>
       </x:c>
       <x:c r="G70" t="n">
-        <x:v>0.1953333333333333</x:v>
+        <x:v>-0.014353333333333334</x:v>
       </x:c>
       <x:c r="H70" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.513</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J70" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K70" t="n">
-        <x:v>46175</x:v>
+      <x:c r="K70" t="str">
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="L70" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M70" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N70" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -23452,7 +23975,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0105</x:v>
       </x:c>
       <x:c r="C71" t="str">
         <x:v>Retatrutide</x:v>
@@ -23461,34 +23984,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E71" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F71" t="n">
-        <x:v>21.4</x:v>
+        <x:v>12.76</x:v>
       </x:c>
       <x:c r="G71" t="n">
-        <x:v>0.06999999999999999</x:v>
+        <x:v>0.27599999999999997</x:v>
       </x:c>
       <x:c r="H71" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.51</x:v>
       </x:c>
       <x:c r="I71" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J71" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="L71" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="M71" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N71" t="str">
-        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -23496,43 +24019,39 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>COA-0051</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>DSIP</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D72" t="str">
-        <x:v>Sleep / Research</x:v>
-      </x:c>
-      <x:c r="E72" t="n">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E72"/>
       <x:c r="F72" t="n">
-        <x:v>10.16</x:v>
-      </x:c>
-      <x:c r="G72" t="n">
-        <x:v>0.016000000000000014</x:v>
-      </x:c>
+        <x:v>22.47</x:v>
+      </x:c>
+      <x:c r="G72"/>
       <x:c r="H72" t="n">
-        <x:v>99.464</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>On label</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="J72" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K72" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>Aminos Analytics</x:v>
+      </x:c>
+      <x:c r="K72" t="n">
+        <x:v>46146</x:v>
       </x:c>
       <x:c r="L72" t="str">
-        <x:v>Red</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M72" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N72" t="str">
-        <x:v>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Labeled quantity unclear from image</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -23540,43 +24059,43 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>COA-0052</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D73" t="str">
-        <x:v>GHRH / GH Secretagogue Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E73" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F73" t="n">
-        <x:v>10.42</x:v>
+        <x:v>17.93</x:v>
       </x:c>
       <x:c r="G73" t="n">
-        <x:v>0.042</x:v>
+        <x:v>0.1953333333333333</x:v>
       </x:c>
       <x:c r="H73" t="n">
-        <x:v>99.446</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J73" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K73" t="n">
-        <x:v>46242</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="L73" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M73" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N73" t="str">
-        <x:v>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -23584,7 +24103,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" t="str">
-        <x:v>COA-0043</x:v>
+        <x:v>COA-0030</x:v>
       </x:c>
       <x:c r="C74" t="str">
         <x:v>Retatrutide</x:v>
@@ -23593,34 +24112,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E74" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F74" t="n">
-        <x:v>10.36</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="G74" t="n">
-        <x:v>0.03599999999999994</x:v>
+        <x:v>0.06999999999999999</x:v>
       </x:c>
       <x:c r="H74" t="n">
-        <x:v>99.41</x:v>
+        <x:v>99.49</x:v>
       </x:c>
       <x:c r="I74" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J74" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K74" t="n">
-        <x:v>46239</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K74" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L74" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M74" t="str">
-        <x:v>Copper</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N74" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -23628,43 +24147,43 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>COA-0077</x:v>
+        <x:v>COA-0051</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>DSIP</x:v>
       </x:c>
       <x:c r="D75" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Sleep / Research</x:v>
       </x:c>
       <x:c r="E75" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F75" t="n">
-        <x:v>10.64</x:v>
+        <x:v>10.16</x:v>
       </x:c>
       <x:c r="G75" t="n">
-        <x:v>0.06400000000000006</x:v>
+        <x:v>0.016000000000000014</x:v>
       </x:c>
       <x:c r="H75" t="n">
-        <x:v>99.4</x:v>
+        <x:v>99.464</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J75" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L75" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M75" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N75" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.4%; net content 10.64 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6DGZ93CS.</x:v>
+        <x:v>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -23672,43 +24191,43 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0052</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
       </x:c>
       <x:c r="D76" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GHRH / GH Secretagogue Blend</x:v>
       </x:c>
       <x:c r="E76" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F76" t="n">
-        <x:v>45.03</x:v>
+        <x:v>10.42</x:v>
       </x:c>
       <x:c r="G76" t="n">
-        <x:v>0.12575</x:v>
+        <x:v>0.042</x:v>
       </x:c>
       <x:c r="H76" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.446</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J76" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K76" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K76" t="n">
+        <x:v>46242</x:v>
       </x:c>
       <x:c r="L76" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M76" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N76" t="str">
-        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -23716,43 +24235,43 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>COA-0098</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>NAD+</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D77" t="str">
-        <x:v>Cellular Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E77" t="n">
-        <x:v>1000</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F77" t="n">
-        <x:v>1006.39</x:v>
+        <x:v>10.36</x:v>
       </x:c>
       <x:c r="G77" t="n">
-        <x:v>0.00639</x:v>
+        <x:v>0.03599999999999994</x:v>
       </x:c>
       <x:c r="H77" t="n">
-        <x:v>99.38</x:v>
+        <x:v>99.41</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J77" t="str">
-        <x:v>PurePoint Analytical</x:v>
-      </x:c>
-      <x:c r="K77" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K77" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L77" t="str">
-        <x:v>Black</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M77" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="N77" t="str">
-        <x:v>Issued 2026-09-21. Batch average 99.38% / 1006.39mg; vial 1 99.77% / 1009.67mg; vial 2 98.98% / 1003.11mg. pH 6.10. Identity confirmed; heavy metals, endotoxin, sterility and fentanyl screens pass.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -23760,34 +24279,34 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>COA-0002</x:v>
+        <x:v>COA-0077</x:v>
       </x:c>
       <x:c r="C78" t="str">
         <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D78" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E78" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F78" t="n">
-        <x:v>10</x:v>
+        <x:v>10.64</x:v>
       </x:c>
       <x:c r="G78" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06400000000000006</x:v>
       </x:c>
       <x:c r="H78" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.4</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J78" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K78" t="n">
-        <x:v>46057</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K78" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L78" t="str">
         <x:v>Not Listed</x:v>
@@ -23796,7 +24315,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N78" t="str">
-        <x:v>On label</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.4%; net content 10.64 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6DGZ93CS.</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -23804,43 +24323,43 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>COA-0049</x:v>
+        <x:v>COA-0104</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>5-Amino-1MQ</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D79" t="str">
-        <x:v>Metabolic / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E79" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F79" t="n">
-        <x:v>51.88</x:v>
+        <x:v>10.94</x:v>
       </x:c>
       <x:c r="G79" t="n">
-        <x:v>0.03760000000000005</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="H79" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.3905</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J79" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-10-27</x:v>
       </x:c>
       <x:c r="L79" t="str">
-        <x:v>Red</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="M79" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N79" t="str">
-        <x:v>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -23848,34 +24367,34 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>COA-0083</x:v>
+        <x:v>COA-0029</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>Tesamorelin</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D80" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E80" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F80" t="n">
-        <x:v>10.24</x:v>
+        <x:v>45.03</x:v>
       </x:c>
       <x:c r="G80" t="n">
-        <x:v>0.02400000000000002</x:v>
+        <x:v>0.12575</x:v>
       </x:c>
       <x:c r="H80" t="n">
-        <x:v>99.36</x:v>
+        <x:v>99.39</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J80" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L80" t="str">
         <x:v>Not Listed</x:v>
@@ -23884,7 +24403,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N80" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.36%; net content 10.24 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code U5SWVSHY.</x:v>
+        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -23892,43 +24411,43 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>COA-0042</x:v>
+        <x:v>COA-0098</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>Ipamorelin</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D81" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Cellular Support</x:v>
       </x:c>
       <x:c r="E81" t="n">
-        <x:v>5</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F81" t="n">
-        <x:v>5.17</x:v>
+        <x:v>1006.39</x:v>
       </x:c>
       <x:c r="G81" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.00639</x:v>
       </x:c>
       <x:c r="H81" t="n">
-        <x:v>99.34</x:v>
+        <x:v>99.38</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K81" t="n">
-        <x:v>46239</x:v>
+        <x:v>PurePoint Analytical</x:v>
+      </x:c>
+      <x:c r="K81" t="str">
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="L81" t="str">
-        <x:v>White</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M81" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N81" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Issued 2026-09-21. Batch average 99.38% / 1006.39mg; vial 1 99.77% / 1009.67mg; vial 2 98.98% / 1003.11mg. pH 6.10. Identity confirmed; heavy metals, endotoxin, sterility and fentanyl screens pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -23936,25 +24455,25 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>COA-0061</x:v>
+        <x:v>COA-0049</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>Sermorelin</x:v>
+        <x:v>5-Amino-1MQ</x:v>
       </x:c>
       <x:c r="D82" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Metabolic / Research</x:v>
       </x:c>
       <x:c r="E82" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F82" t="n">
-        <x:v>10.41</x:v>
+        <x:v>51.88</x:v>
       </x:c>
       <x:c r="G82" t="n">
-        <x:v>0.040999999999999995</x:v>
+        <x:v>0.03760000000000005</x:v>
       </x:c>
       <x:c r="H82" t="n">
-        <x:v>99.335</x:v>
+        <x:v>99.369</x:v>
       </x:c>
       <x:c r="I82" t="str">
         <x:v>On label</x:v>
@@ -23963,16 +24482,16 @@
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L82" t="str">
-        <x:v>Green</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M82" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N82" t="str">
-        <x:v>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -23980,43 +24499,43 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>COA-0039</x:v>
+        <x:v>COA-0002</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D83" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E83" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F83" t="n">
-        <x:v>5.07</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G83" t="n">
-        <x:v>0.014000000000000058</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H83" t="n">
-        <x:v>99.32</x:v>
+        <x:v>99.369</x:v>
       </x:c>
       <x:c r="I83" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J83" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K83" t="n">
-        <x:v>46239</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L83" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M83" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N83" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>On label</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -24024,43 +24543,43 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>COA-0048</x:v>
+        <x:v>COA-0083</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>Tesamorelin</x:v>
       </x:c>
       <x:c r="D84" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E84" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F84" t="n">
-        <x:v>51.52</x:v>
+        <x:v>10.24</x:v>
       </x:c>
       <x:c r="G84" t="n">
-        <x:v>0.030400000000000062</x:v>
+        <x:v>0.02400000000000002</x:v>
       </x:c>
       <x:c r="H84" t="n">
-        <x:v>99.32</x:v>
+        <x:v>99.36</x:v>
       </x:c>
       <x:c r="I84" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J84" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L84" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M84" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N84" t="str">
-        <x:v>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.36%; net content 10.24 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code U5SWVSHY.</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -24068,43 +24587,43 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>COA-0074</x:v>
+        <x:v>COA-0042</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="D85" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E85" t="n">
-        <x:v>40</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F85" t="n">
-        <x:v>41.09</x:v>
+        <x:v>5.17</x:v>
       </x:c>
       <x:c r="G85" t="n">
-        <x:v>0.027250000000000087</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H85" t="n">
-        <x:v>99.3</x:v>
+        <x:v>99.34</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K85" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K85" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L85" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>White</x:v>
       </x:c>
       <x:c r="M85" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N85" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.3%; net content 41.09 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code SQG57YUA.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -24112,43 +24631,43 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>COA-0076</x:v>
+        <x:v>COA-0061</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>NAD+</x:v>
+        <x:v>Sermorelin</x:v>
       </x:c>
       <x:c r="D86" t="str">
-        <x:v>Cellular / Metabolic Research</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E86" t="n">
-        <x:v>1000</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F86" t="n">
-        <x:v>1047.39</x:v>
+        <x:v>10.41</x:v>
       </x:c>
       <x:c r="G86" t="n">
-        <x:v>0.0473900000000001</x:v>
+        <x:v>0.040999999999999995</x:v>
       </x:c>
       <x:c r="H86" t="n">
-        <x:v>99.26</x:v>
+        <x:v>99.335</x:v>
       </x:c>
       <x:c r="I86" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J86" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>08/18/2026</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="L86" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M86" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N86" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.26%; net content 1047.39 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code EKUVZRXB.</x:v>
+        <x:v>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -24156,43 +24675,43 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" t="str">
-        <x:v>COA-0053</x:v>
+        <x:v>COA-0048</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D87" t="str">
-        <x:v>Cosmetic / Recovery</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E87" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F87" t="n">
-        <x:v>100.52</x:v>
+        <x:v>51.52</x:v>
       </x:c>
       <x:c r="G87" t="n">
-        <x:v>0.0052</x:v>
+        <x:v>0.030400000000000062</x:v>
       </x:c>
       <x:c r="H87" t="n">
-        <x:v>99.25</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="I87" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J87" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K87" t="n">
-        <x:v>46224</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K87" t="str">
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L87" t="str">
-        <x:v>Light Blue</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M87" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N87" t="str">
-        <x:v>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</x:v>
+        <x:v>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -24200,25 +24719,25 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>COA-0062</x:v>
+        <x:v>COA-0039</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D88" t="str">
-        <x:v>Cosmetic / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E88" t="n">
-        <x:v>50</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F88" t="n">
-        <x:v>52.48</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="G88" t="n">
-        <x:v>0.0496</x:v>
+        <x:v>0.014000000000000058</x:v>
       </x:c>
       <x:c r="H88" t="n">
-        <x:v>99.25</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="I88" t="str">
         <x:v>On label</x:v>
@@ -24226,8 +24745,8 @@
       <x:c r="J88" t="str">
         <x:v>SteriGenix</x:v>
       </x:c>
-      <x:c r="K88" t="str">
-        <x:v>2026-08-26</x:v>
+      <x:c r="K88" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L88" t="str">
         <x:v>Blue</x:v>
@@ -24236,7 +24755,7 @@
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N88" t="str">
-        <x:v>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -24244,25 +24763,25 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>COA-0072</x:v>
+        <x:v>COA-0074</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>KPV</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D89" t="str">
-        <x:v>Healing / Anti-Inflammatory Research</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E89" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F89" t="n">
-        <x:v>10.23</x:v>
+        <x:v>41.09</x:v>
       </x:c>
       <x:c r="G89" t="n">
-        <x:v>0.02300000000000004</x:v>
+        <x:v>0.027250000000000087</x:v>
       </x:c>
       <x:c r="H89" t="n">
-        <x:v>99.25</x:v>
+        <x:v>99.3</x:v>
       </x:c>
       <x:c r="I89" t="str">
         <x:v>On label</x:v>
@@ -24280,7 +24799,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N89" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.25%; net content 10.23 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code XXW57EWE.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.3%; net content 41.09 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code SQG57YUA.</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -24288,43 +24807,43 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>COA-0091</x:v>
+        <x:v>COA-0076</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D90" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Cellular / Metabolic Research</x:v>
       </x:c>
       <x:c r="E90" t="n">
-        <x:v>30</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F90" t="n">
-        <x:v>32.14</x:v>
+        <x:v>1047.39</x:v>
       </x:c>
       <x:c r="G90" t="n">
-        <x:v>0.07133333333333333</x:v>
+        <x:v>0.0473900000000001</x:v>
       </x:c>
       <x:c r="H90" t="n">
-        <x:v>99.233</x:v>
+        <x:v>99.26</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J90" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>08/18/2026</x:v>
       </x:c>
       <x:c r="L90" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M90" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N90" t="str">
-        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.233%; batch average net content 32.14 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.307% / 32.51 mg and 99.158% / 31.77 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.26%; net content 1047.39 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code EKUVZRXB.</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -24332,25 +24851,25 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>COA-0065</x:v>
+        <x:v>COA-0072</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D91" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Healing / Anti-Inflammatory Research</x:v>
       </x:c>
       <x:c r="E91" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F91" t="n">
-        <x:v>10.28</x:v>
+        <x:v>10.23</x:v>
       </x:c>
       <x:c r="G91" t="n">
-        <x:v>0.027999999999999935</x:v>
+        <x:v>0.02300000000000004</x:v>
       </x:c>
       <x:c r="H91" t="n">
-        <x:v>99.21</x:v>
+        <x:v>99.25</x:v>
       </x:c>
       <x:c r="I91" t="str">
         <x:v>On label</x:v>
@@ -24368,7 +24887,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N91" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.21%; net content 10.28 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code DNPTRN59.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.25%; net content 10.23 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code XXW57EWE.</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -24376,43 +24895,43 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>COA-0086</x:v>
+        <x:v>COA-0062</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D92" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E92" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F92" t="n">
-        <x:v>22.06</x:v>
+        <x:v>52.48</x:v>
       </x:c>
       <x:c r="G92" t="n">
-        <x:v>0.10300000000000001</x:v>
+        <x:v>0.0496</x:v>
       </x:c>
       <x:c r="H92" t="n">
-        <x:v>99.16</x:v>
+        <x:v>99.25</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J92" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="L92" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M92" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N92" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.16%; net content 22.06 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.16% / 22.26 mg and 99.15% / 21.85 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -24420,43 +24939,43 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" t="str">
-        <x:v>COA-0037</x:v>
+        <x:v>COA-0053</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>BPC-157 / TB-500 Blend</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D93" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E93" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F93" t="n">
-        <x:v>10.55</x:v>
+        <x:v>100.52</x:v>
       </x:c>
       <x:c r="G93" t="n">
-        <x:v>0.05500000000000007</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
       <x:c r="H93" t="n">
-        <x:v>99.13</x:v>
+        <x:v>99.25</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J93" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K93" t="n">
-        <x:v>46239</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="L93" t="str">
-        <x:v>Red</x:v>
+        <x:v>Light Blue</x:v>
       </x:c>
       <x:c r="M93" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N93" t="str">
-        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -24464,43 +24983,43 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0091</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D94" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E94" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F94" t="n">
-        <x:v>11.38</x:v>
+        <x:v>32.14</x:v>
       </x:c>
       <x:c r="G94" t="n">
-        <x:v>0.1380000000000001</x:v>
+        <x:v>0.07133333333333333</x:v>
       </x:c>
       <x:c r="H94" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.233</x:v>
       </x:c>
       <x:c r="I94" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J94" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K94" t="n">
-        <x:v>46155</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K94" t="str">
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="L94" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M94" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N94" t="str">
-        <x:v>TB-500 / TB4</x:v>
+        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.233%; batch average net content 32.14 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.307% / 32.51 mg and 99.158% / 31.77 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -24508,25 +25027,25 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>COA-0073</x:v>
+        <x:v>COA-0065</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="D95" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>Metabolic / Fat Loss</x:v>
       </x:c>
       <x:c r="E95" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F95" t="n">
-        <x:v>10.42</x:v>
+        <x:v>10.28</x:v>
       </x:c>
       <x:c r="G95" t="n">
-        <x:v>0.041999999999999996</x:v>
+        <x:v>0.027999999999999935</x:v>
       </x:c>
       <x:c r="H95" t="n">
-        <x:v>99.08</x:v>
+        <x:v>99.21</x:v>
       </x:c>
       <x:c r="I95" t="str">
         <x:v>On label</x:v>
@@ -24544,7 +25063,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N95" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.08%; net content 10.42 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 26KYBWZX.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.21%; net content 10.28 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code DNPTRN59.</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -24552,43 +25071,43 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0086</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D96" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E96" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F96" t="n">
-        <x:v>11.17</x:v>
+        <x:v>22.06</x:v>
       </x:c>
       <x:c r="G96" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.10300000000000001</x:v>
       </x:c>
       <x:c r="H96" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.16</x:v>
       </x:c>
       <x:c r="I96" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J96" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K96" t="n">
-        <x:v>46155</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L96" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M96" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N96" t="str">
-        <x:v>MS10 / MOTS-C</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.16%; net content 22.06 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.16% / 22.26 mg and 99.15% / 21.85 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -24596,43 +25115,43 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>COA-0100</x:v>
+        <x:v>COA-0037</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>Tesamorelin</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="D97" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E97" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F97" t="n">
-        <x:v>11.34</x:v>
+        <x:v>10.55</x:v>
       </x:c>
       <x:c r="G97" t="n">
-        <x:v>0.134</x:v>
+        <x:v>0.05500000000000007</x:v>
       </x:c>
       <x:c r="H97" t="n">
-        <x:v>99.05</x:v>
+        <x:v>99.13</x:v>
       </x:c>
       <x:c r="I97" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J97" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K97" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K97" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L97" t="str">
-        <x:v>Black</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M97" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N97" t="str">
-        <x:v>Samples 99.06% / 11.37mg and 99.04% / 11.30mg; reported mean 99.05% / 11.34mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -24640,28 +25159,28 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="C98" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="D98" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E98" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F98" t="n">
-        <x:v>10.47</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="G98" t="n">
-        <x:v>0.04700000000000006</x:v>
+        <x:v>0.1380000000000001</x:v>
       </x:c>
       <x:c r="H98" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J98" t="str">
         <x:v>Janoshik</x:v>
@@ -24676,7 +25195,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N98" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>TB-500 / TB4</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -24684,25 +25203,25 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" t="str">
-        <x:v>COA-0064</x:v>
+        <x:v>COA-0073</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>AHK-Cu</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D99" t="str">
-        <x:v>Cosmetic / Skin Research</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E99" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F99" t="n">
-        <x:v>51.12</x:v>
+        <x:v>10.42</x:v>
       </x:c>
       <x:c r="G99" t="n">
-        <x:v>0.022399999999999948</x:v>
+        <x:v>0.041999999999999996</x:v>
       </x:c>
       <x:c r="H99" t="n">
-        <x:v>98.64</x:v>
+        <x:v>99.08</x:v>
       </x:c>
       <x:c r="I99" t="str">
         <x:v>On label</x:v>
@@ -24720,7 +25239,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N99" t="str">
-        <x:v>Identity confirmed; HPLC purity 98.64%; net content 51.12 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6ZNHW4J7.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.08%; net content 10.42 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 26KYBWZX.</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -24728,24 +25247,26 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" t="str">
-        <x:v>COA-0017</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="C100" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D100" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E100" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F100" t="n">
-        <x:v>5.54</x:v>
+        <x:v>11.17</x:v>
       </x:c>
       <x:c r="G100" t="n">
-        <x:v>0.108</x:v>
-      </x:c>
-      <x:c r="H100"/>
+        <x:v>0.117</x:v>
+      </x:c>
+      <x:c r="H100" t="n">
+        <x:v>99.055</x:v>
+      </x:c>
       <x:c r="I100" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
@@ -24753,7 +25274,7 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K100" t="n">
-        <x:v>46057</x:v>
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="L100" t="str">
         <x:v>Not Listed</x:v>
@@ -24762,7 +25283,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N100" t="str">
-        <x:v>Blend report BPC5+TB5</x:v>
+        <x:v>MS10 / MOTS-C</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -24770,41 +25291,43 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" t="str">
-        <x:v>COA-0018</x:v>
+        <x:v>COA-0100</x:v>
       </x:c>
       <x:c r="C101" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Tesamorelin</x:v>
       </x:c>
       <x:c r="D101" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E101" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F101" t="n">
-        <x:v>5.43</x:v>
+        <x:v>11.34</x:v>
       </x:c>
       <x:c r="G101" t="n">
-        <x:v>0.08599999999999994</x:v>
-      </x:c>
-      <x:c r="H101"/>
+        <x:v>0.134</x:v>
+      </x:c>
+      <x:c r="H101" t="n">
+        <x:v>99.05</x:v>
+      </x:c>
       <x:c r="I101" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J101" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K101" t="n">
-        <x:v>46057</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="L101" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M101" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N101" t="str">
-        <x:v>Blend report BPC5+TB5</x:v>
+        <x:v>Samples 99.06% / 11.37mg and 99.04% / 11.30mg; reported mean 99.05% / 11.34mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -24812,34 +25335,206 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B102" t="str">
+        <x:v>COA-0011</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Cagrilintide</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E102" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F102" t="n">
+        <x:v>10.47</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>0.04700000000000006</x:v>
+      </x:c>
+      <x:c r="H102" t="n">
+        <x:v>99.04</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K102" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L102" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M102" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N102" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>COA-0064</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>AHK-Cu</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>Cosmetic / Skin Research</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>51.12</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.022399999999999948</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>98.64</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>08/17/2026</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>Identity confirmed; HPLC purity 98.64%; net content 51.12 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6ZNHW4J7.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>COA-0018</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>5.43</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.08599999999999994</x:v>
+      </x:c>
+      <x:c r="H104"/>
+      <x:c r="I104" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K104" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>COA-0017</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>5.54</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.108</x:v>
+      </x:c>
+      <x:c r="H105"/>
+      <x:c r="I105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
         <x:v>COA-0095</x:v>
       </x:c>
-      <x:c r="C102" t="str">
+      <x:c r="C106" t="str">
         <x:v>hCG 5000 IU</x:v>
       </x:c>
-      <x:c r="D102" t="str">
+      <x:c r="D106" t="str">
         <x:v>Hormone Research</x:v>
       </x:c>
-      <x:c r="E102"/>
-      <x:c r="F102"/>
-      <x:c r="G102"/>
-      <x:c r="H102"/>
-      <x:c r="I102" t="str">
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+      <x:c r="G106"/>
+      <x:c r="H106"/>
+      <x:c r="I106" t="str">
         <x:v>Review (IU; see notes)</x:v>
       </x:c>
-      <x:c r="J102" t="str">
+      <x:c r="J106" t="str">
         <x:v>Chromate</x:v>
       </x:c>
-      <x:c r="K102" t="str">
+      <x:c r="K106" t="str">
         <x:v>2026-10-12</x:v>
       </x:c>
-      <x:c r="L102" t="str">
+      <x:c r="L106" t="str">
         <x:v>Red</x:v>
       </x:c>
-      <x:c r="M102" t="str">
+      <x:c r="M106" t="str">
         <x:v>Silver</x:v>
       </x:c>
-      <x:c r="N102" t="str">
+      <x:c r="N106" t="str">
         <x:v>Labeled quantity 5000 IU; measured quantity 6288 IU (25.76% above label). These are IU, NOT mg; mg fields deliberately blank. HPLC-UV potency estimate has approximately +/-15% margin of error. Purity not reported. Identity: hCG. Received 2026-09-29.</x:v>
       </x:c>
     </x:row>
@@ -33600,6 +34295,278 @@
         <x:v>Purple cap / silver crimp visible or listed in supplied report.</x:v>
       </x:c>
     </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="V103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -35435,10 +36402,8 @@
           <x:t xml:space="preserve">Freedom Diagnostics</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GHK-Cu, KLOW 80mg, Retatrutide</x:t>
-        </x:is>
+      <x:c r="B4" t="str">
+        <x:v>GHK-Cu, KLOW 80mg, Retatrutide, NAD+</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr">
         <x:is>
@@ -35567,10 +36532,8 @@
           <x:t xml:space="preserve">Tianjin Qiangxin (third-party partner lab)</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Eloralintide</x:t>
-        </x:is>
+      <x:c r="B10" t="str">
+        <x:v>Eloralintide, Retatrutide</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
@@ -43458,6 +44421,254 @@
       </x:c>
       <x:c r="T102" t="str">
         <x:v>Reported 2026-10-14. BPC-157 acetate; HPLC VWD SOP-043: potency 24.36%, 243.62mg/g, 19.66mg/unit. Expanded uncertainty +/-7.81% at 95% confidence. No sterility or endotoxin results supplied.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -51921,6 +53132,266 @@
         <x:v>Purple cap / silver crimp visible or listed in supplied report.</x:v>
       </x:c>
     </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="K103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="L103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="M103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="U103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="J104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="K104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="L104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="M104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="U104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="K105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="L105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="M105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="F106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="G106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="H106" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="K106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="L106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="M106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -54709,6 +56180,794 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>White</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
